--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.25</v>
+        <v>0.4715447154471545</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.3333333333333333</v>
+        <v>0.4710144927536232</v>
       </c>
       <c r="D2">
-        <v>0.8</v>
+        <v>0.5572519083969466</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>123</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,22 +420,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.4715447154471545</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4710144927536232</v>
+        <v>0.489051094890511</v>
       </c>
       <c r="D2">
-        <v>0.5572519083969466</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="E2">
         <v>123</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2">
         <v>7</v>
